--- a/Баллы 2026.xlsx
+++ b/Баллы 2026.xlsx
@@ -519,6 +519,21 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -530,21 +545,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -993,7 +993,7 @@
         <f>L1+7</f>
         <v>44132</v>
       </c>
-      <c r="O1" s="48">
+      <c r="O1" s="44">
         <f>N1+7</f>
         <v>44139</v>
       </c>
@@ -1054,7 +1054,7 @@
       </c>
     </row>
     <row r="2" spans="1:34" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="42" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="14">
@@ -1063,9 +1063,15 @@
       <c r="C2" s="15">
         <v>1</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="D2" s="16">
+        <v>5</v>
+      </c>
+      <c r="E2" s="16">
+        <v>1</v>
+      </c>
+      <c r="F2" s="16">
+        <v>1</v>
+      </c>
       <c r="G2" s="37"/>
       <c r="H2" s="34"/>
       <c r="I2" s="16"/>
@@ -1074,7 +1080,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="16"/>
       <c r="N2" s="34"/>
-      <c r="O2" s="49"/>
+      <c r="O2" s="45"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="39"/>
       <c r="R2" s="16"/>
@@ -1088,7 +1094,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA11" si="0">SUM(C2:Z2)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB2" s="18" t="str">
         <f t="shared" ref="AB2:AB11" si="1">IF(AA2&gt;=87,"отл",IF(AA2&gt;=73,"хорошо",IF(AA2&gt;=50,"удовл","Не удовл")))</f>
@@ -1107,7 +1113,7 @@
       </c>
     </row>
     <row r="3" spans="1:34" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="43" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="14">
@@ -1116,9 +1122,15 @@
       <c r="C3" s="15">
         <v>1</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="D3" s="16">
+        <v>5</v>
+      </c>
+      <c r="E3" s="16">
+        <v>0</v>
+      </c>
+      <c r="F3" s="16">
+        <v>1</v>
+      </c>
       <c r="G3" s="37"/>
       <c r="H3" s="34"/>
       <c r="I3" s="16"/>
@@ -1127,7 +1139,7 @@
       <c r="L3" s="37"/>
       <c r="M3" s="16"/>
       <c r="N3" s="34"/>
-      <c r="O3" s="49"/>
+      <c r="O3" s="45"/>
       <c r="P3" s="16"/>
       <c r="Q3" s="40"/>
       <c r="R3" s="16"/>
@@ -1141,7 +1153,7 @@
       <c r="Z3" s="20"/>
       <c r="AA3" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB3" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1160,7 +1172,7 @@
       </c>
     </row>
     <row r="4" spans="1:34" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="42" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="14">
@@ -1169,18 +1181,26 @@
       <c r="C4" s="15">
         <v>1</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="D4" s="16">
+        <v>5</v>
+      </c>
+      <c r="E4" s="16">
+        <v>1</v>
+      </c>
+      <c r="F4" s="16">
+        <v>1</v>
+      </c>
       <c r="G4" s="37"/>
       <c r="H4" s="34"/>
-      <c r="I4" s="16"/>
+      <c r="I4" s="16">
+        <v>8</v>
+      </c>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
       <c r="L4" s="37"/>
       <c r="M4" s="16"/>
       <c r="N4" s="34"/>
-      <c r="O4" s="49"/>
+      <c r="O4" s="45"/>
       <c r="P4" s="16"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="16"/>
@@ -1194,7 +1214,7 @@
       <c r="Z4" s="20"/>
       <c r="AA4" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AB4" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1213,7 +1233,7 @@
       </c>
     </row>
     <row r="5" spans="1:34" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="43" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="14">
@@ -1222,9 +1242,15 @@
       <c r="C5" s="15">
         <v>1</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="D5" s="16">
+        <v>5</v>
+      </c>
+      <c r="E5" s="16">
+        <v>1</v>
+      </c>
+      <c r="F5" s="16">
+        <v>1</v>
+      </c>
       <c r="G5" s="37"/>
       <c r="H5" s="34"/>
       <c r="I5" s="16"/>
@@ -1233,7 +1259,7 @@
       <c r="L5" s="37"/>
       <c r="M5" s="16"/>
       <c r="N5" s="34"/>
-      <c r="O5" s="49"/>
+      <c r="O5" s="45"/>
       <c r="P5" s="16"/>
       <c r="Q5" s="40"/>
       <c r="R5" s="16"/>
@@ -1247,7 +1273,7 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB5" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1266,7 +1292,7 @@
       </c>
     </row>
     <row r="6" spans="1:34" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="42" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="14">
@@ -1275,18 +1301,26 @@
       <c r="C6" s="15">
         <v>1</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
+      <c r="D6" s="16">
+        <v>5</v>
+      </c>
+      <c r="E6" s="16">
+        <v>1</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1</v>
+      </c>
       <c r="G6" s="37"/>
       <c r="H6" s="34"/>
-      <c r="I6" s="16"/>
+      <c r="I6" s="16">
+        <v>8</v>
+      </c>
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
       <c r="L6" s="37"/>
       <c r="M6" s="16"/>
       <c r="N6" s="34"/>
-      <c r="O6" s="49"/>
+      <c r="O6" s="45"/>
       <c r="P6" s="16"/>
       <c r="Q6" s="39"/>
       <c r="R6" s="16"/>
@@ -1300,7 +1334,7 @@
       <c r="Z6" s="17"/>
       <c r="AA6" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AB6" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1319,7 +1353,7 @@
       </c>
     </row>
     <row r="7" spans="1:34" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="43" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="14">
@@ -1328,9 +1362,15 @@
       <c r="C7" s="15">
         <v>1</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
+      <c r="D7" s="16">
+        <v>5</v>
+      </c>
+      <c r="E7" s="16">
+        <v>1</v>
+      </c>
+      <c r="F7" s="16">
+        <v>0</v>
+      </c>
       <c r="G7" s="37"/>
       <c r="H7" s="34"/>
       <c r="I7" s="16"/>
@@ -1339,7 +1379,7 @@
       <c r="L7" s="37"/>
       <c r="M7" s="16"/>
       <c r="N7" s="34"/>
-      <c r="O7" s="49"/>
+      <c r="O7" s="45"/>
       <c r="P7" s="16"/>
       <c r="Q7" s="40"/>
       <c r="R7" s="16"/>
@@ -1353,7 +1393,7 @@
       <c r="Z7" s="20"/>
       <c r="AA7" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB7" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1372,7 +1412,7 @@
       </c>
     </row>
     <row r="8" spans="1:34" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="42" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="14">
@@ -1381,18 +1421,26 @@
       <c r="C8" s="15">
         <v>1</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="D8" s="16">
+        <v>5</v>
+      </c>
+      <c r="E8" s="16">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1</v>
+      </c>
       <c r="G8" s="37"/>
       <c r="H8" s="34"/>
-      <c r="I8" s="16"/>
+      <c r="I8" s="16">
+        <v>8</v>
+      </c>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
       <c r="L8" s="37"/>
       <c r="M8" s="23"/>
       <c r="N8" s="34"/>
-      <c r="O8" s="49"/>
+      <c r="O8" s="45"/>
       <c r="P8" s="16"/>
       <c r="Q8" s="39"/>
       <c r="R8" s="16"/>
@@ -1406,7 +1454,7 @@
       <c r="Z8" s="17"/>
       <c r="AA8" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1425,7 +1473,7 @@
       </c>
     </row>
     <row r="9" spans="1:34" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="43" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="14">
@@ -1434,9 +1482,15 @@
       <c r="C9" s="25">
         <v>1</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
+      <c r="D9" s="23">
+        <v>5</v>
+      </c>
+      <c r="E9" s="23">
+        <v>1</v>
+      </c>
+      <c r="F9" s="23">
+        <v>1</v>
+      </c>
       <c r="G9" s="37"/>
       <c r="H9" s="35"/>
       <c r="I9" s="23"/>
@@ -1445,7 +1499,7 @@
       <c r="L9" s="37"/>
       <c r="M9" s="23"/>
       <c r="N9" s="35"/>
-      <c r="O9" s="50"/>
+      <c r="O9" s="46"/>
       <c r="P9" s="23"/>
       <c r="Q9" s="41"/>
       <c r="R9" s="23"/>
@@ -1459,7 +1513,7 @@
       <c r="Z9" s="26"/>
       <c r="AA9" s="12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB9" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1493,7 +1547,7 @@
       <c r="L10" s="37"/>
       <c r="M10" s="16"/>
       <c r="N10" s="34"/>
-      <c r="O10" s="49"/>
+      <c r="O10" s="45"/>
       <c r="P10" s="16"/>
       <c r="Q10" s="39"/>
       <c r="R10" s="16"/>
@@ -1542,7 +1596,7 @@
       <c r="L11" s="37"/>
       <c r="M11" s="16"/>
       <c r="N11" s="34"/>
-      <c r="O11" s="49"/>
+      <c r="O11" s="45"/>
       <c r="P11" s="16"/>
       <c r="Q11" s="40"/>
       <c r="R11" s="16"/>
@@ -1577,44 +1631,44 @@
     <row r="12" spans="1:34" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="28"/>
       <c r="B12" s="29"/>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="44" t="s">
+      <c r="D12" s="47"/>
+      <c r="E12" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="45" t="s">
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45" t="s">
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45" t="s">
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="42" t="s">
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="W12" s="42"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="43" t="s">
+      <c r="W12" s="47"/>
+      <c r="X12" s="47"/>
+      <c r="Y12" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="Z12" s="43"/>
+      <c r="Z12" s="48"/>
       <c r="AA12" s="12"/>
       <c r="AB12" s="30"/>
       <c r="AC12" s="31"/>
@@ -1649,7 +1703,7 @@
       <c r="L23" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cUq+qdrmw6ijXy445KjTA+Yxw4SYUVX+v/LRHvVfLDNKOxdVLCqvJ9kz/0M9mJuMNWT/TtFscfroDqKcDzFwjg==" saltValue="Rfcf97OgA9e8NT3DflExCg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yrbNvK3cSshvx7vupeXpbwKNpYte4EMzDEtr9cTmhbg2mTfUV+Waai/4++Kaf7oQ3+ua2gpVECHH5p2yj9G2+A==" saltValue="QxtMjzv6iZy1Jx+2ON/xSw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:Z12"/>

--- a/Баллы 2026.xlsx
+++ b/Баллы 2026.xlsx
@@ -1074,7 +1074,9 @@
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="34"/>
-      <c r="I2" s="16"/>
+      <c r="I2" s="16">
+        <v>8</v>
+      </c>
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
       <c r="L2" s="37"/>
@@ -1094,7 +1096,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA11" si="0">SUM(C2:Z2)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AB2" s="18" t="str">
         <f t="shared" ref="AB2:AB11" si="1">IF(AA2&gt;=87,"отл",IF(AA2&gt;=73,"хорошо",IF(AA2&gt;=50,"удовл","Не удовл")))</f>
@@ -1703,7 +1705,7 @@
       <c r="L23" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yrbNvK3cSshvx7vupeXpbwKNpYte4EMzDEtr9cTmhbg2mTfUV+Waai/4++Kaf7oQ3+ua2gpVECHH5p2yj9G2+A==" saltValue="QxtMjzv6iZy1Jx+2ON/xSw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dxiGbq82Uwr1EmU4fmuRxLFunySHBBbXkhTSB38BlnnJPv0YMGQD0UtYGEevmTxMIisW66pKfNl2GcOgI75nfg==" saltValue="3JUh7wptZlj1UMp986jkTA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:Z12"/>

--- a/Баллы 2026.xlsx
+++ b/Баллы 2026.xlsx
@@ -1072,8 +1072,12 @@
       <c r="F2" s="16">
         <v>1</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
+      <c r="G2" s="37">
+        <v>1</v>
+      </c>
+      <c r="H2" s="34">
+        <v>1</v>
+      </c>
       <c r="I2" s="16">
         <v>8</v>
       </c>
@@ -1096,7 +1100,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA11" si="0">SUM(C2:Z2)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB2" s="18" t="str">
         <f t="shared" ref="AB2:AB11" si="1">IF(AA2&gt;=87,"отл",IF(AA2&gt;=73,"хорошо",IF(AA2&gt;=50,"удовл","Не удовл")))</f>
@@ -1133,9 +1137,15 @@
       <c r="F3" s="16">
         <v>1</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="16"/>
+      <c r="G3" s="37">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34">
+        <v>1</v>
+      </c>
+      <c r="I3" s="16">
+        <v>8</v>
+      </c>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
       <c r="L3" s="37"/>
@@ -1155,7 +1165,7 @@
       <c r="Z3" s="20"/>
       <c r="AA3" s="12">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1192,8 +1202,12 @@
       <c r="F4" s="16">
         <v>1</v>
       </c>
-      <c r="G4" s="37"/>
-      <c r="H4" s="34"/>
+      <c r="G4" s="37">
+        <v>1</v>
+      </c>
+      <c r="H4" s="34">
+        <v>1</v>
+      </c>
       <c r="I4" s="16">
         <v>8</v>
       </c>
@@ -1216,7 +1230,7 @@
       <c r="Z4" s="20"/>
       <c r="AA4" s="12">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB4" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1253,9 +1267,15 @@
       <c r="F5" s="16">
         <v>1</v>
       </c>
-      <c r="G5" s="37"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="16"/>
+      <c r="G5" s="37">
+        <v>1</v>
+      </c>
+      <c r="H5" s="34">
+        <v>1</v>
+      </c>
+      <c r="I5" s="16">
+        <v>8</v>
+      </c>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
       <c r="L5" s="37"/>
@@ -1275,7 +1295,7 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="12">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AB5" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1312,8 +1332,12 @@
       <c r="F6" s="16">
         <v>1</v>
       </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="34"/>
+      <c r="G6" s="37">
+        <v>1</v>
+      </c>
+      <c r="H6" s="34">
+        <v>1</v>
+      </c>
       <c r="I6" s="16">
         <v>8</v>
       </c>
@@ -1336,7 +1360,7 @@
       <c r="Z6" s="17"/>
       <c r="AA6" s="12">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB6" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1373,9 +1397,15 @@
       <c r="F7" s="16">
         <v>0</v>
       </c>
-      <c r="G7" s="37"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="16"/>
+      <c r="G7" s="37">
+        <v>1</v>
+      </c>
+      <c r="H7" s="34">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16">
+        <v>8</v>
+      </c>
       <c r="J7" s="16"/>
       <c r="K7" s="16"/>
       <c r="L7" s="37"/>
@@ -1395,7 +1425,7 @@
       <c r="Z7" s="20"/>
       <c r="AA7" s="12">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AB7" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1432,8 +1462,12 @@
       <c r="F8" s="16">
         <v>1</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="34"/>
+      <c r="G8" s="37">
+        <v>1</v>
+      </c>
+      <c r="H8" s="34">
+        <v>1</v>
+      </c>
       <c r="I8" s="16">
         <v>8</v>
       </c>
@@ -1456,7 +1490,7 @@
       <c r="Z8" s="17"/>
       <c r="AA8" s="12">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB8" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1493,9 +1527,15 @@
       <c r="F9" s="23">
         <v>1</v>
       </c>
-      <c r="G9" s="37"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="23"/>
+      <c r="G9" s="37">
+        <v>1</v>
+      </c>
+      <c r="H9" s="35">
+        <v>0</v>
+      </c>
+      <c r="I9" s="23">
+        <v>8</v>
+      </c>
       <c r="J9" s="23"/>
       <c r="K9" s="23"/>
       <c r="L9" s="37"/>
@@ -1515,7 +1555,7 @@
       <c r="Z9" s="26"/>
       <c r="AA9" s="12">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AB9" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1705,7 +1745,7 @@
       <c r="L23" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dxiGbq82Uwr1EmU4fmuRxLFunySHBBbXkhTSB38BlnnJPv0YMGQD0UtYGEevmTxMIisW66pKfNl2GcOgI75nfg==" saltValue="3JUh7wptZlj1UMp986jkTA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IkscO2PRrhnLg6Fmwrbv2mmULSlo2lIpVO8klBSg9JxD5pZRyY8ya0tIXwXIL6QKfPG8M6KMY1xm9NeqXMCDQQ==" saltValue="/KEU/N3rPeavtnXdG2IAhA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:Z12"/>

--- a/Баллы 2026.xlsx
+++ b/Баллы 2026.xlsx
@@ -1081,7 +1081,9 @@
       <c r="I2" s="16">
         <v>8</v>
       </c>
-      <c r="J2" s="16"/>
+      <c r="J2" s="16">
+        <v>1</v>
+      </c>
       <c r="K2" s="16"/>
       <c r="L2" s="37"/>
       <c r="M2" s="16"/>
@@ -1100,7 +1102,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA11" si="0">SUM(C2:Z2)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB2" s="18" t="str">
         <f t="shared" ref="AB2:AB11" si="1">IF(AA2&gt;=87,"отл",IF(AA2&gt;=73,"хорошо",IF(AA2&gt;=50,"удовл","Не удовл")))</f>
@@ -1146,7 +1148,9 @@
       <c r="I3" s="16">
         <v>8</v>
       </c>
-      <c r="J3" s="16"/>
+      <c r="J3" s="16">
+        <v>1</v>
+      </c>
       <c r="K3" s="16"/>
       <c r="L3" s="37"/>
       <c r="M3" s="16"/>
@@ -1165,7 +1169,7 @@
       <c r="Z3" s="20"/>
       <c r="AA3" s="12">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1211,7 +1215,9 @@
       <c r="I4" s="16">
         <v>8</v>
       </c>
-      <c r="J4" s="16"/>
+      <c r="J4" s="16">
+        <v>1</v>
+      </c>
       <c r="K4" s="16"/>
       <c r="L4" s="37"/>
       <c r="M4" s="16"/>
@@ -1230,7 +1236,7 @@
       <c r="Z4" s="20"/>
       <c r="AA4" s="12">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB4" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1276,7 +1282,9 @@
       <c r="I5" s="16">
         <v>8</v>
       </c>
-      <c r="J5" s="16"/>
+      <c r="J5" s="16">
+        <v>1</v>
+      </c>
       <c r="K5" s="16"/>
       <c r="L5" s="37"/>
       <c r="M5" s="16"/>
@@ -1295,7 +1303,7 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="12">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB5" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1341,7 +1349,9 @@
       <c r="I6" s="16">
         <v>8</v>
       </c>
-      <c r="J6" s="16"/>
+      <c r="J6" s="16">
+        <v>1</v>
+      </c>
       <c r="K6" s="16"/>
       <c r="L6" s="37"/>
       <c r="M6" s="16"/>
@@ -1360,7 +1370,7 @@
       <c r="Z6" s="17"/>
       <c r="AA6" s="12">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB6" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1406,7 +1416,9 @@
       <c r="I7" s="16">
         <v>8</v>
       </c>
-      <c r="J7" s="16"/>
+      <c r="J7" s="16">
+        <v>1</v>
+      </c>
       <c r="K7" s="16"/>
       <c r="L7" s="37"/>
       <c r="M7" s="16"/>
@@ -1425,7 +1437,7 @@
       <c r="Z7" s="20"/>
       <c r="AA7" s="12">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1471,7 +1483,9 @@
       <c r="I8" s="16">
         <v>8</v>
       </c>
-      <c r="J8" s="16"/>
+      <c r="J8" s="16">
+        <v>1</v>
+      </c>
       <c r="K8" s="16"/>
       <c r="L8" s="37"/>
       <c r="M8" s="23"/>
@@ -1490,7 +1504,7 @@
       <c r="Z8" s="17"/>
       <c r="AA8" s="12">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB8" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1536,7 +1550,9 @@
       <c r="I9" s="23">
         <v>8</v>
       </c>
-      <c r="J9" s="23"/>
+      <c r="J9" s="23">
+        <v>1</v>
+      </c>
       <c r="K9" s="23"/>
       <c r="L9" s="37"/>
       <c r="M9" s="23"/>
@@ -1555,7 +1571,7 @@
       <c r="Z9" s="26"/>
       <c r="AA9" s="12">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB9" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1745,7 +1761,7 @@
       <c r="L23" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="IkscO2PRrhnLg6Fmwrbv2mmULSlo2lIpVO8klBSg9JxD5pZRyY8ya0tIXwXIL6QKfPG8M6KMY1xm9NeqXMCDQQ==" saltValue="/KEU/N3rPeavtnXdG2IAhA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="anaigSfc94C+q1x+oY9h97Fopn+cYTOsfEH7a90UK82MKw8CaAe5ed8drj2dElfE1bbii3s2/QOfhS+Kh2X1KQ==" saltValue="sT4LPKsRASphuXYwTcH+gw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:Z12"/>

--- a/Баллы 2026.xlsx
+++ b/Баллы 2026.xlsx
@@ -1084,7 +1084,9 @@
       <c r="J2" s="16">
         <v>1</v>
       </c>
-      <c r="K2" s="16"/>
+      <c r="K2" s="16">
+        <v>1</v>
+      </c>
       <c r="L2" s="37"/>
       <c r="M2" s="16"/>
       <c r="N2" s="34"/>
@@ -1102,7 +1104,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA11" si="0">SUM(C2:Z2)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB2" s="18" t="str">
         <f t="shared" ref="AB2:AB11" si="1">IF(AA2&gt;=87,"отл",IF(AA2&gt;=73,"хорошо",IF(AA2&gt;=50,"удовл","Не удовл")))</f>
@@ -1151,7 +1153,9 @@
       <c r="J3" s="16">
         <v>1</v>
       </c>
-      <c r="K3" s="16"/>
+      <c r="K3" s="16">
+        <v>0</v>
+      </c>
       <c r="L3" s="37"/>
       <c r="M3" s="16"/>
       <c r="N3" s="34"/>
@@ -1218,9 +1222,13 @@
       <c r="J4" s="16">
         <v>1</v>
       </c>
-      <c r="K4" s="16"/>
+      <c r="K4" s="16">
+        <v>1</v>
+      </c>
       <c r="L4" s="37"/>
-      <c r="M4" s="16"/>
+      <c r="M4" s="16">
+        <v>11</v>
+      </c>
       <c r="N4" s="34"/>
       <c r="O4" s="45"/>
       <c r="P4" s="16"/>
@@ -1236,7 +1244,7 @@
       <c r="Z4" s="20"/>
       <c r="AA4" s="12">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AB4" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1285,7 +1293,9 @@
       <c r="J5" s="16">
         <v>1</v>
       </c>
-      <c r="K5" s="16"/>
+      <c r="K5" s="16">
+        <v>1</v>
+      </c>
       <c r="L5" s="37"/>
       <c r="M5" s="16"/>
       <c r="N5" s="34"/>
@@ -1303,7 +1313,7 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="12">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB5" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1352,9 +1362,13 @@
       <c r="J6" s="16">
         <v>1</v>
       </c>
-      <c r="K6" s="16"/>
+      <c r="K6" s="16">
+        <v>1</v>
+      </c>
       <c r="L6" s="37"/>
-      <c r="M6" s="16"/>
+      <c r="M6" s="16">
+        <v>11</v>
+      </c>
       <c r="N6" s="34"/>
       <c r="O6" s="45"/>
       <c r="P6" s="16"/>
@@ -1370,7 +1384,7 @@
       <c r="Z6" s="17"/>
       <c r="AA6" s="12">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AB6" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1419,7 +1433,9 @@
       <c r="J7" s="16">
         <v>1</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="16">
+        <v>1</v>
+      </c>
       <c r="L7" s="37"/>
       <c r="M7" s="16"/>
       <c r="N7" s="34"/>
@@ -1437,7 +1453,7 @@
       <c r="Z7" s="20"/>
       <c r="AA7" s="12">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB7" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1486,7 +1502,9 @@
       <c r="J8" s="16">
         <v>1</v>
       </c>
-      <c r="K8" s="16"/>
+      <c r="K8" s="16">
+        <v>1</v>
+      </c>
       <c r="L8" s="37"/>
       <c r="M8" s="23"/>
       <c r="N8" s="34"/>
@@ -1504,7 +1522,7 @@
       <c r="Z8" s="17"/>
       <c r="AA8" s="12">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB8" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1553,9 +1571,13 @@
       <c r="J9" s="23">
         <v>1</v>
       </c>
-      <c r="K9" s="23"/>
+      <c r="K9" s="23">
+        <v>1</v>
+      </c>
       <c r="L9" s="37"/>
-      <c r="M9" s="23"/>
+      <c r="M9" s="23">
+        <v>11</v>
+      </c>
       <c r="N9" s="35"/>
       <c r="O9" s="46"/>
       <c r="P9" s="23"/>
@@ -1571,7 +1593,7 @@
       <c r="Z9" s="26"/>
       <c r="AA9" s="12">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AB9" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1761,7 +1783,7 @@
       <c r="L23" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="anaigSfc94C+q1x+oY9h97Fopn+cYTOsfEH7a90UK82MKw8CaAe5ed8drj2dElfE1bbii3s2/QOfhS+Kh2X1KQ==" saltValue="sT4LPKsRASphuXYwTcH+gw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PKUglCzJ/FHJmPjHidmnzkniF9ImYgo0GXLuGJRIWqT1Kju7Wu854Q8+o8ObkxWV/lKPd7QsiEaKLbtFRvm7gw==" saltValue="yrsQVflYiQoaE6mThTNEMQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:Z12"/>

--- a/Баллы 2026.xlsx
+++ b/Баллы 2026.xlsx
@@ -1087,8 +1087,12 @@
       <c r="K2" s="16">
         <v>1</v>
       </c>
-      <c r="L2" s="37"/>
-      <c r="M2" s="16"/>
+      <c r="L2" s="37">
+        <v>1</v>
+      </c>
+      <c r="M2" s="16">
+        <v>11</v>
+      </c>
       <c r="N2" s="34"/>
       <c r="O2" s="45"/>
       <c r="P2" s="16"/>
@@ -1104,7 +1108,7 @@
       <c r="Z2" s="17"/>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA11" si="0">SUM(C2:Z2)</f>
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AB2" s="18" t="str">
         <f t="shared" ref="AB2:AB11" si="1">IF(AA2&gt;=87,"отл",IF(AA2&gt;=73,"хорошо",IF(AA2&gt;=50,"удовл","Не удовл")))</f>
@@ -1156,8 +1160,12 @@
       <c r="K3" s="16">
         <v>0</v>
       </c>
-      <c r="L3" s="37"/>
-      <c r="M3" s="16"/>
+      <c r="L3" s="37">
+        <v>1</v>
+      </c>
+      <c r="M3" s="16">
+        <v>11</v>
+      </c>
       <c r="N3" s="34"/>
       <c r="O3" s="45"/>
       <c r="P3" s="16"/>
@@ -1173,7 +1181,7 @@
       <c r="Z3" s="20"/>
       <c r="AA3" s="12">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AB3" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1225,7 +1233,9 @@
       <c r="K4" s="16">
         <v>1</v>
       </c>
-      <c r="L4" s="37"/>
+      <c r="L4" s="37">
+        <v>1</v>
+      </c>
       <c r="M4" s="16">
         <v>11</v>
       </c>
@@ -1244,7 +1254,7 @@
       <c r="Z4" s="20"/>
       <c r="AA4" s="12">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AB4" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1296,8 +1306,12 @@
       <c r="K5" s="16">
         <v>1</v>
       </c>
-      <c r="L5" s="37"/>
-      <c r="M5" s="16"/>
+      <c r="L5" s="37">
+        <v>1</v>
+      </c>
+      <c r="M5" s="16">
+        <v>8</v>
+      </c>
       <c r="N5" s="34"/>
       <c r="O5" s="45"/>
       <c r="P5" s="16"/>
@@ -1313,7 +1327,7 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="12">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AB5" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1365,7 +1379,9 @@
       <c r="K6" s="16">
         <v>1</v>
       </c>
-      <c r="L6" s="37"/>
+      <c r="L6" s="37">
+        <v>1</v>
+      </c>
       <c r="M6" s="16">
         <v>11</v>
       </c>
@@ -1384,7 +1400,7 @@
       <c r="Z6" s="17"/>
       <c r="AA6" s="12">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AB6" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1436,8 +1452,12 @@
       <c r="K7" s="16">
         <v>1</v>
       </c>
-      <c r="L7" s="37"/>
-      <c r="M7" s="16"/>
+      <c r="L7" s="37">
+        <v>1</v>
+      </c>
+      <c r="M7" s="16">
+        <v>11</v>
+      </c>
       <c r="N7" s="34"/>
       <c r="O7" s="45"/>
       <c r="P7" s="16"/>
@@ -1453,7 +1473,7 @@
       <c r="Z7" s="20"/>
       <c r="AA7" s="12">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AB7" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1505,8 +1525,12 @@
       <c r="K8" s="16">
         <v>1</v>
       </c>
-      <c r="L8" s="37"/>
-      <c r="M8" s="23"/>
+      <c r="L8" s="37">
+        <v>1</v>
+      </c>
+      <c r="M8" s="23">
+        <v>11</v>
+      </c>
       <c r="N8" s="34"/>
       <c r="O8" s="45"/>
       <c r="P8" s="16"/>
@@ -1522,7 +1546,7 @@
       <c r="Z8" s="17"/>
       <c r="AA8" s="12">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AB8" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1574,7 +1598,9 @@
       <c r="K9" s="23">
         <v>1</v>
       </c>
-      <c r="L9" s="37"/>
+      <c r="L9" s="37">
+        <v>1</v>
+      </c>
       <c r="M9" s="23">
         <v>11</v>
       </c>
@@ -1593,7 +1619,7 @@
       <c r="Z9" s="26"/>
       <c r="AA9" s="12">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AB9" s="22" t="str">
         <f t="shared" si="1"/>
@@ -1783,7 +1809,7 @@
       <c r="L23" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PKUglCzJ/FHJmPjHidmnzkniF9ImYgo0GXLuGJRIWqT1Kju7Wu854Q8+o8ObkxWV/lKPd7QsiEaKLbtFRvm7gw==" saltValue="yrsQVflYiQoaE6mThTNEMQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="clN26oxa4hHT7e3wkFvQkodZxtQhe1rZ+DZIi9BB6La0WuaeeeDDXBTnbjCo1C0TcGsPjTxXy2n7DaPO4fi9Zg==" saltValue="xJ3Xv9icl2nYBVey//Ut2A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:Z12"/>
